--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487410_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487410_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7502</v>
+        <v>5.3852</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9803</v>
+        <v>3.5085</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7698</v>
+        <v>1.8768</v>
       </c>
       <c r="G2" t="n">
         <v>2.6025</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4599</v>
+        <v>2.0949</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6068</v>
+        <v>2.1349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1469</v>
+        <v>-0.04</v>
       </c>
       <c r="V2" t="n">
         <v>0.8837</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0638</v>
+        <v>2.9537</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3064</v>
+        <v>1.4287</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2426</v>
+        <v>1.5249</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438</v>
+        <v>0.6133</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7009</v>
+        <v>1.3711</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2629</v>
+        <v>-0.7579</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5254</v>
+        <v>1.0498</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1268</v>
+        <v>1.8388</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6014</v>
+        <v>-0.789</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0874</v>
+        <v>-0.4365</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4259</v>
+        <v>-0.4677</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6615</v>
+        <v>0.0311</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5875</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6257</v>
+        <v>1.8116</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8766</v>
+        <v>1.925</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7492</v>
+        <v>-0.1134</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6083</v>
+        <v>0.3329</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8837</v>
+        <v>0.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5546</v>
+        <v>1.1545</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0029</v>
+        <v>3.7714</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5517</v>
+        <v>-2.6169</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6133</v>
+        <v>0.438</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3711</v>
+        <v>1.7009</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7579</v>
+        <v>-1.2629</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0498</v>
+        <v>2.5254</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8388</v>
+        <v>3.1268</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.789</v>
+        <v>-0.6014</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4365</v>
+        <v>-2.0874</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4677</v>
+        <v>-1.4259</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0311</v>
+        <v>-0.6615</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3502</v>
+        <v>0.5875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4125</v>
+        <v>1.7165</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4991</v>
+        <v>1.3415</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0866</v>
+        <v>0.3749</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3329</v>
+        <v>-0.6083</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6083</v>
+        <v>0.8837</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>M. PEREIRA NIETO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6149</v>
+        <v>-0.1022</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3308</v>
+        <v>-1.9539</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9457</v>
+        <v>1.8516</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2707</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.1053</v>
+        <v>0.4339</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8346</v>
+        <v>0.5454</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.4528</v>
+        <v>0.0076</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.1803</v>
+        <v>0.837</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7275</v>
+        <v>-0.8294</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1821</v>
+        <v>0.9718</v>
       </c>
       <c r="N5" t="n">
-        <v>0.075</v>
+        <v>-0.4031</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1072</v>
+        <v>1.3749</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1751</v>
+        <v>-2.9377</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8695</v>
+        <v>0.6811</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2971</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5724</v>
+        <v>-0.2952</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8858</v>
+        <v>-0.6485</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7572</v>
+        <v>-2.4932</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8714</v>
+        <v>1.8447</v>
       </c>
       <c r="G6" t="n">
         <v>-1.657</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4543</v>
+        <v>1.6916</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0433</v>
+        <v>1.3074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4109</v>
+        <v>0.3842</v>
       </c>
       <c r="V6" t="n">
         <v>0.8837</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. PEREIRA NIETO</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8963</v>
+        <v>-1.0244</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3203</v>
+        <v>-2.5424</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4239</v>
+        <v>1.518</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9792999999999999</v>
+        <v>-2.2707</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4339</v>
+        <v>-4.1053</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5454</v>
+        <v>1.8346</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0076</v>
+        <v>-3.4528</v>
       </c>
       <c r="K7" t="n">
-        <v>0.837</v>
+        <v>-4.1803</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8294</v>
+        <v>0.7275</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9718</v>
+        <v>1.1821</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4031</v>
+        <v>0.075</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3749</v>
+        <v>1.1072</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9377</v>
+        <v>-1.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.113</v>
+        <v>2.2302</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6099</v>
+        <v>2.0855</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7229</v>
+        <v>0.1447</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1581</v>
+        <v>-1.5712</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9756</v>
+        <v>-0.1979</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1825</v>
+        <v>-1.3734</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1139</v>
+        <v>1.127</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7554</v>
+        <v>0.8693</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3585</v>
+        <v>0.2577</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5806</v>
+        <v>2.1104</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.621</v>
+        <v>1.6109</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0404</v>
+        <v>0.4994</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5333</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1344</v>
+        <v>-0.7416</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.399</v>
+        <v>-0.2417</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5875</v>
+        <v>-4.3087</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-6.0713</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4567</v>
+        <v>0.7268</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4158</v>
+        <v>1.0545</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0409</v>
+        <v>-0.3277</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.7086</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3725</v>
+        <v>-1.8824</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5447</v>
+        <v>-1.5663</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8278</v>
+        <v>-0.3162</v>
       </c>
       <c r="G9" t="n">
-        <v>1.127</v>
+        <v>-1.1139</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8693</v>
+        <v>-0.7554</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2577</v>
+        <v>-0.3585</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1104</v>
+        <v>-0.5806</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6109</v>
+        <v>-0.621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4994</v>
+        <v>0.0404</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.5333</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7416</v>
+        <v>-0.1344</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2417</v>
+        <v>-0.399</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.3087</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0713</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0745</v>
+        <v>-0.181</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2923</v>
+        <v>-0.0065</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7822</v>
+        <v>-0.1745</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7086</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,19 +1189,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.6708</v>
+        <v>4.264700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6389999999999993</v>
+        <v>-0.0450999999999997</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3096</v>
+        <v>4.3095</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7185</v>
+        <v>0.7184999999999997</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3955</v>
+        <v>3.395500000000001</v>
       </c>
       <c r="I10" t="n">
         <v>-2.6771</v>
@@ -1210,22 +1210,22 @@
         <v>1.5367</v>
       </c>
       <c r="K10" t="n">
-        <v>5.0516</v>
+        <v>5.051600000000001</v>
       </c>
       <c r="L10" t="n">
         <v>-3.515</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8181000000000003</v>
+        <v>-0.8181000000000005</v>
       </c>
       <c r="N10" t="n">
         <v>-1.6561</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8379999999999996</v>
+        <v>0.8379999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.8339</v>
+        <v>-7.833900000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>-19.5847</v>
@@ -1234,16 +1234,16 @@
         <v>11.7509</v>
       </c>
       <c r="S10" t="n">
-        <v>10.1777</v>
+        <v>10.7717</v>
       </c>
       <c r="T10" t="n">
-        <v>10.2247</v>
+        <v>10.8186</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.04700000000000015</v>
+        <v>-0.04700000000000007</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6084000000000001</v>
+        <v>0.6084000000000002</v>
       </c>
       <c r="W10" t="n">
         <v>7.1846</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.7144</v>
+        <v>7.8051</v>
       </c>
       <c r="E11" t="n">
-        <v>5.175</v>
+        <v>5.4476</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5394</v>
+        <v>2.3574</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7843</v>
+        <v>5.3288</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1469</v>
+        <v>3.7326</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6374</v>
+        <v>1.5962</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8105</v>
+        <v>4.431</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0022</v>
+        <v>3.9316</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8083</v>
+        <v>0.4994</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9738</v>
+        <v>0.8978</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1448</v>
+        <v>-0.199</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8290999999999999</v>
+        <v>1.0968</v>
       </c>
       <c r="P11" t="n">
-        <v>1.9585</v>
+        <v>2.7419</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9377</v>
+        <v>2.7419</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7513</v>
+        <v>-1.3055</v>
       </c>
       <c r="T11" t="n">
-        <v>2.793</v>
+        <v>-0.2</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0418</v>
+        <v>-1.1055</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2203</v>
+        <v>1.0399</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5507</v>
+        <v>1.2166</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3304</v>
+        <v>-0.1767</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8675</v>
+        <v>5.5498</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8336</v>
+        <v>3.4353</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0339</v>
+        <v>2.1145</v>
       </c>
       <c r="G12" t="n">
-        <v>5.3288</v>
+        <v>3.7843</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7326</v>
+        <v>2.1469</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5962</v>
+        <v>1.6374</v>
       </c>
       <c r="J12" t="n">
-        <v>4.431</v>
+        <v>2.8105</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9316</v>
+        <v>2.0022</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4994</v>
+        <v>0.8083</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8978</v>
+        <v>0.9738</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.199</v>
+        <v>0.1448</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0968</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7419</v>
+        <v>1.9585</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7419</v>
+        <v>2.9377</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2431</v>
+        <v>-0.4133</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8139999999999999</v>
+        <v>1.0533</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4291</v>
+        <v>-1.4667</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0399</v>
+        <v>0.2203</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2166</v>
+        <v>0.5507</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1767</v>
+        <v>-0.3304</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1205</v>
+        <v>0.7313</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5678</v>
+        <v>-0.3632</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4473</v>
+        <v>1.0945</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9136</v>
@@ -1468,13 +1468,13 @@
         <v>3.3294</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8135</v>
+        <v>-1.9617</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.554</v>
+        <v>-0.3494</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2595</v>
+        <v>-1.6124</v>
       </c>
       <c r="V13" t="n">
         <v>2.2565</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3948</v>
+        <v>-1.2611</v>
       </c>
       <c r="E14" t="n">
         <v>-0.8789</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5158</v>
+        <v>-0.3822</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6735</v>
@@ -1546,13 +1546,13 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7955</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3388</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1217</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BLAS</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0395</v>
+        <v>-1.5529</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3397</v>
+        <v>-1.8134</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3001</v>
+        <v>0.2606</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9983</v>
+        <v>-1.1745</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3413</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.657</v>
+        <v>-0.3181</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9317</v>
+        <v>-1.1901</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2591</v>
+        <v>-0.5887</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6726</v>
+        <v>-0.6014</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0666</v>
+        <v>0.0156</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0822</v>
+        <v>-0.2677</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0156</v>
+        <v>0.2833</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6288</v>
+        <v>-1.141</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0371</v>
+        <v>0.0806</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5917</v>
+        <v>-1.2216</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6083</v>
+        <v>-0.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.184</v>
+        <v>-1.9185</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7834</v>
+        <v>-0.6811</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4006</v>
+        <v>-1.2374</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0176</v>
@@ -1702,13 +1702,13 @@
         <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2198</v>
+        <v>0.0457</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1012</v>
+        <v>0.0012</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1186</v>
+        <v>0.0446</v>
       </c>
       <c r="V16" t="n">
         <v>-1.3383</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>M. GONZALEZ BLAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4831</v>
+        <v>-1.9879</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5298</v>
+        <v>-2.2373</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0467</v>
+        <v>0.2495</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1745</v>
+        <v>-2.9983</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-2.3413</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3181</v>
+        <v>-0.657</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1901</v>
+        <v>-1.9317</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5887</v>
+        <v>-1.2591</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6014</v>
+        <v>-0.6726</v>
       </c>
       <c r="M17" t="n">
+        <v>-1.0666</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1.0822</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.0156</v>
       </c>
-      <c r="N17" t="n">
-        <v>-0.2677</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.2833</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.0712</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6358</v>
+        <v>0.0653</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4354</v>
+        <v>-0.6424</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6083</v>
+        <v>0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5476</v>
+        <v>-3.334</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4842</v>
+        <v>-2.3029</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0634</v>
+        <v>-1.031</v>
       </c>
       <c r="G18" t="n">
         <v>0.593</v>
@@ -1858,13 +1858,13 @@
         <v>2.546</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.101</v>
+        <v>-0.8874</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9116</v>
+        <v>0.0929</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0126</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6687</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-7.483</v>
+        <v>-6.338</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.7344</v>
+        <v>-4.9157</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7486</v>
+        <v>-1.4223</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6471</v>
@@ -1936,13 +1936,13 @@
         <v>3.1336</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.0562</v>
+        <v>-1.9111</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1769</v>
+        <v>-0.3582</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.8793</v>
+        <v>-1.553</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9963</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.670599999999998</v>
+        <v>-2.3062</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3096</v>
+        <v>-4.309600000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6389999999999996</v>
+        <v>2.0036</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7185000000000006</v>
@@ -1990,10 +1990,10 @@
         <v>0.8181000000000003</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6562</v>
+        <v>1.656199999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8378999999999998</v>
+        <v>-0.8379</v>
       </c>
       <c r="M20" t="n">
         <v>-1.5367</v>
@@ -2014,13 +2014,13 @@
         <v>19.5848</v>
       </c>
       <c r="S20" t="n">
-        <v>-10.1778</v>
+        <v>-8.8132</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04679999999999995</v>
+        <v>0.0469</v>
       </c>
       <c r="U20" t="n">
-        <v>-10.2247</v>
+        <v>-8.860299999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6083000000000005</v>
